--- a/E1_refereestats.xlsx
+++ b/E1_refereestats.xlsx
@@ -209,55 +209,58 @@
     <t>John Busby</t>
   </si>
   <si>
+    <t>Andrew Kitchen</t>
+  </si>
+  <si>
+    <t>Stephen Martin</t>
+  </si>
+  <si>
+    <t>Gavin Ward</t>
+  </si>
+  <si>
+    <t>Dean Whitestone</t>
+  </si>
+  <si>
+    <t>Matt Donohue</t>
+  </si>
+  <si>
+    <t>Samuel Allison</t>
+  </si>
+  <si>
+    <t>James Bell</t>
+  </si>
+  <si>
+    <t>Tom Nield</t>
+  </si>
+  <si>
     <t>Joshua Smith</t>
   </si>
   <si>
-    <t>Andrew Kitchen</t>
-  </si>
-  <si>
-    <t>Gavin Ward</t>
-  </si>
-  <si>
-    <t>Dean Whitestone</t>
-  </si>
-  <si>
-    <t>James Bell</t>
-  </si>
-  <si>
-    <t>Matt Donohue</t>
-  </si>
-  <si>
-    <t>Samuel Allison</t>
-  </si>
-  <si>
-    <t>Tom Nield</t>
-  </si>
-  <si>
-    <t>Stephen Martin</t>
-  </si>
-  <si>
     <t>Robert Madley</t>
   </si>
   <si>
+    <t>Andrew Davies</t>
+  </si>
+  <si>
+    <t>James Linington</t>
+  </si>
+  <si>
+    <t>Lewis Smith</t>
+  </si>
+  <si>
     <t>Anthony Backhouse</t>
   </si>
   <si>
-    <t>Lewis Smith</t>
-  </si>
-  <si>
-    <t>James Linington</t>
+    <t>Leigh Doughty</t>
+  </si>
+  <si>
+    <t>Ben Toner</t>
   </si>
   <si>
     <t>Will Finnie</t>
   </si>
   <si>
-    <t>Andrew Davies</t>
-  </si>
-  <si>
-    <t>Leigh Doughty</t>
-  </si>
-  <si>
-    <t>Ben Toner</t>
+    <t>Farai Hallam</t>
   </si>
   <si>
     <t/>
@@ -266,19 +269,34 @@
     <t>Thomas Bramall</t>
   </si>
   <si>
-    <t>Farai Hallam</t>
+    <t>Darren Bond</t>
+  </si>
+  <si>
+    <t>Jeremy Simpson</t>
+  </si>
+  <si>
+    <t>Tim Robinson</t>
+  </si>
+  <si>
+    <t>Tony Harrington</t>
   </si>
   <si>
     <t>Michael Salisbury</t>
   </si>
   <si>
-    <t>Tim Robinson</t>
-  </si>
-  <si>
     <t>Thomas Kirk</t>
   </si>
   <si>
-    <t>Darren Bond</t>
+    <t>Adam Herczeg</t>
+  </si>
+  <si>
+    <t>Ruebyn Ricardo</t>
+  </si>
+  <si>
+    <t>Elliot Bell</t>
+  </si>
+  <si>
+    <t>Jarred Gillett</t>
   </si>
   <si>
     <t>Geoff Eltringham</t>
@@ -287,22 +305,19 @@
     <t>Sunny Gill</t>
   </si>
   <si>
-    <t>Adam Herczeg</t>
-  </si>
-  <si>
-    <t>Jarred Gillett</t>
-  </si>
-  <si>
     <t>Simon Hooper</t>
   </si>
   <si>
-    <t>Tony Harrington</t>
+    <t>Ben Speedie</t>
   </si>
   <si>
     <t>Stuart Attwell</t>
   </si>
   <si>
-    <t>Ruebyn Ricardo</t>
+    <t>Robert Jones</t>
+  </si>
+  <si>
+    <t>Craig Pawson</t>
   </si>
   <si>
     <t>Andy Madley</t>
@@ -314,15 +329,6 @@
     <t>John Brooks</t>
   </si>
   <si>
-    <t>Elliot Bell</t>
-  </si>
-  <si>
-    <t>Robert Jones</t>
-  </si>
-  <si>
-    <t>Craig Pawson</t>
-  </si>
-  <si>
     <t>Steve Martin</t>
   </si>
   <si>
@@ -339,12 +345,6 @@
   </si>
   <si>
     <t>Samuel Barrott</t>
-  </si>
-  <si>
-    <t>Ben Speedie</t>
-  </si>
-  <si>
-    <t>Jeremy Simpson</t>
   </si>
 </sst>
 </file>
@@ -442,40 +442,40 @@
         <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="D2" t="n">
-        <v>770.0</v>
+        <v>1045.0</v>
       </c>
       <c r="E2" t="n">
-        <v>36.666666666666664</v>
+        <v>38.7037037037037</v>
       </c>
       <c r="F2" t="n">
-        <v>8200.0</v>
+        <v>12625.0</v>
       </c>
       <c r="G2" t="n">
-        <v>390.4761904761905</v>
+        <v>467.5925925925926</v>
       </c>
       <c r="H2" t="n">
-        <v>3300.0</v>
+        <v>11925.0</v>
       </c>
       <c r="I2" t="n">
-        <v>157.14285714285714</v>
+        <v>441.6666666666667</v>
       </c>
       <c r="J2" t="n">
-        <v>23.047619047619047</v>
+        <v>47.370370370370374</v>
       </c>
       <c r="K2" t="n">
-        <v>16.285714285714285</v>
+        <v>36.7037037037037</v>
       </c>
       <c r="L2" t="n">
-        <v>17.666666666666668</v>
+        <v>39.81481481481482</v>
       </c>
       <c r="M2" t="n">
         <v>22.0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.6142557651991614</v>
+        <v>1.71875</v>
       </c>
     </row>
     <row r="3">
@@ -486,40 +486,40 @@
         <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0</v>
+        <v>26.0</v>
       </c>
       <c r="D3" t="n">
-        <v>560.0</v>
+        <v>735.0</v>
       </c>
       <c r="E3" t="n">
-        <v>28.0</v>
+        <v>28.26923076923077</v>
       </c>
       <c r="F3" t="n">
-        <v>4100.0</v>
+        <v>5250.0</v>
       </c>
       <c r="G3" t="n">
-        <v>205.0</v>
+        <v>201.92307692307693</v>
       </c>
       <c r="H3" t="n">
-        <v>2400.0</v>
+        <v>3700.0</v>
       </c>
       <c r="I3" t="n">
-        <v>120.0</v>
+        <v>142.30769230769232</v>
       </c>
       <c r="J3" t="n">
-        <v>22.1</v>
+        <v>36.30769230769231</v>
       </c>
       <c r="K3" t="n">
-        <v>28.45</v>
+        <v>45.84615384615385</v>
       </c>
       <c r="L3" t="n">
-        <v>16.9</v>
+        <v>39.76923076923077</v>
       </c>
       <c r="M3" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3365155131264916</v>
+        <v>1.3339382940108893</v>
       </c>
     </row>
     <row r="4">
@@ -530,40 +530,40 @@
         <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="D4" t="n">
-        <v>650.0</v>
+        <v>810.0</v>
       </c>
       <c r="E4" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="F4" t="n">
-        <v>5450.0</v>
+        <v>6050.0</v>
       </c>
       <c r="G4" t="n">
-        <v>272.5</v>
+        <v>242.0</v>
       </c>
       <c r="H4" t="n">
-        <v>3300.0</v>
+        <v>5100.0</v>
       </c>
       <c r="I4" t="n">
-        <v>165.0</v>
+        <v>204.0</v>
       </c>
       <c r="J4" t="n">
-        <v>28.05</v>
+        <v>41.32</v>
       </c>
       <c r="K4" t="n">
-        <v>22.4</v>
+        <v>35.88</v>
       </c>
       <c r="L4" t="n">
-        <v>27.75</v>
+        <v>42.64</v>
       </c>
       <c r="M4" t="n">
         <v>21.0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5402843601895735</v>
+        <v>1.542857142857143</v>
       </c>
     </row>
     <row r="5">
@@ -574,40 +574,40 @@
         <v>65</v>
       </c>
       <c r="C5" t="n">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="D5" t="n">
-        <v>815.0</v>
+        <v>835.0</v>
       </c>
       <c r="E5" t="n">
-        <v>42.89473684210526</v>
+        <v>34.791666666666664</v>
       </c>
       <c r="F5" t="n">
-        <v>8000.0</v>
+        <v>9850.0</v>
       </c>
       <c r="G5" t="n">
-        <v>421.05263157894734</v>
+        <v>410.4166666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>4550.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I5" t="n">
-        <v>239.47368421052633</v>
+        <v>250.0</v>
       </c>
       <c r="J5" t="n">
-        <v>19.31578947368421</v>
+        <v>38.25</v>
       </c>
       <c r="K5" t="n">
-        <v>24.894736842105264</v>
+        <v>42.166666666666664</v>
       </c>
       <c r="L5" t="n">
-        <v>21.36842105263158</v>
+        <v>47.208333333333336</v>
       </c>
       <c r="M5" t="n">
-        <v>21.0</v>
+        <v>25.0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.9591346153846154</v>
+        <v>1.3733552631578947</v>
       </c>
     </row>
     <row r="6">
@@ -618,40 +618,40 @@
         <v>66</v>
       </c>
       <c r="C6" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="D6" t="n">
-        <v>675.0</v>
+        <v>945.0</v>
       </c>
       <c r="E6" t="n">
-        <v>37.5</v>
+        <v>39.375</v>
       </c>
       <c r="F6" t="n">
-        <v>7950.0</v>
+        <v>11550.0</v>
       </c>
       <c r="G6" t="n">
-        <v>441.6666666666667</v>
+        <v>481.25</v>
       </c>
       <c r="H6" t="n">
-        <v>3500.0</v>
+        <v>11500.0</v>
       </c>
       <c r="I6" t="n">
-        <v>194.44444444444446</v>
+        <v>479.1666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>28.72222222222222</v>
+        <v>29.5</v>
       </c>
       <c r="K6" t="n">
-        <v>25.055555555555557</v>
+        <v>30.375</v>
       </c>
       <c r="L6" t="n">
-        <v>29.72222222222222</v>
+        <v>30.916666666666668</v>
       </c>
       <c r="M6" t="n">
         <v>25.0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4610389610389611</v>
+        <v>1.575</v>
       </c>
     </row>
     <row r="7">
@@ -662,40 +662,40 @@
         <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="D7" t="n">
-        <v>890.0</v>
+        <v>1045.0</v>
       </c>
       <c r="E7" t="n">
-        <v>49.44444444444444</v>
+        <v>43.541666666666664</v>
       </c>
       <c r="F7" t="n">
-        <v>11575.0</v>
+        <v>12775.0</v>
       </c>
       <c r="G7" t="n">
-        <v>643.0555555555555</v>
+        <v>532.2916666666666</v>
       </c>
       <c r="H7" t="n">
-        <v>6650.0</v>
+        <v>8950.0</v>
       </c>
       <c r="I7" t="n">
-        <v>369.44444444444446</v>
+        <v>372.9166666666667</v>
       </c>
       <c r="J7" t="n">
-        <v>25.11111111111111</v>
+        <v>44.166666666666664</v>
       </c>
       <c r="K7" t="n">
-        <v>34.72222222222222</v>
+        <v>47.833333333333336</v>
       </c>
       <c r="L7" t="n">
-        <v>20.61111111111111</v>
+        <v>35.916666666666664</v>
       </c>
       <c r="M7" t="n">
         <v>22.0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1601941747572817</v>
+        <v>1.9569288389513109</v>
       </c>
     </row>
     <row r="8">
@@ -706,40 +706,40 @@
         <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="D8" t="n">
-        <v>655.0</v>
+        <v>835.0</v>
       </c>
       <c r="E8" t="n">
-        <v>36.388888888888886</v>
+        <v>34.791666666666664</v>
       </c>
       <c r="F8" t="n">
-        <v>6700.0</v>
+        <v>8400.0</v>
       </c>
       <c r="G8" t="n">
-        <v>372.22222222222223</v>
+        <v>350.0</v>
       </c>
       <c r="H8" t="n">
-        <v>4000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="I8" t="n">
-        <v>222.22222222222223</v>
+        <v>312.5</v>
       </c>
       <c r="J8" t="n">
-        <v>19.666666666666668</v>
+        <v>37.625</v>
       </c>
       <c r="K8" t="n">
-        <v>27.61111111111111</v>
+        <v>44.041666666666664</v>
       </c>
       <c r="L8" t="n">
-        <v>24.11111111111111</v>
+        <v>42.125</v>
       </c>
       <c r="M8" t="n">
         <v>23.0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5707434052757794</v>
+        <v>1.5099457504520795</v>
       </c>
     </row>
     <row r="9">
@@ -750,40 +750,40 @@
         <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="D9" t="n">
-        <v>880.0</v>
+        <v>1085.0</v>
       </c>
       <c r="E9" t="n">
-        <v>48.888888888888886</v>
+        <v>45.208333333333336</v>
       </c>
       <c r="F9" t="n">
-        <v>12450.0</v>
+        <v>13925.0</v>
       </c>
       <c r="G9" t="n">
-        <v>691.6666666666666</v>
+        <v>580.2083333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>5900.0</v>
+        <v>9675.0</v>
       </c>
       <c r="I9" t="n">
-        <v>327.77777777777777</v>
+        <v>403.125</v>
       </c>
       <c r="J9" t="n">
-        <v>16.0</v>
+        <v>35.208333333333336</v>
       </c>
       <c r="K9" t="n">
-        <v>18.22222222222222</v>
+        <v>43.041666666666664</v>
       </c>
       <c r="L9" t="n">
-        <v>11.666666666666666</v>
+        <v>34.375</v>
       </c>
       <c r="M9" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.100238663484487</v>
+        <v>2.0018450184501844</v>
       </c>
     </row>
     <row r="10">
@@ -794,40 +794,40 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="D10" t="n">
-        <v>795.0</v>
+        <v>940.0</v>
       </c>
       <c r="E10" t="n">
-        <v>44.166666666666664</v>
+        <v>40.869565217391305</v>
       </c>
       <c r="F10" t="n">
-        <v>9075.0</v>
+        <v>10500.0</v>
       </c>
       <c r="G10" t="n">
-        <v>504.1666666666667</v>
+        <v>456.5217391304348</v>
       </c>
       <c r="H10" t="n">
-        <v>7075.0</v>
+        <v>8800.0</v>
       </c>
       <c r="I10" t="n">
-        <v>393.05555555555554</v>
+        <v>382.60869565217394</v>
       </c>
       <c r="J10" t="n">
-        <v>16.166666666666668</v>
+        <v>33.391304347826086</v>
       </c>
       <c r="K10" t="n">
-        <v>23.27777777777778</v>
+        <v>40.0</v>
       </c>
       <c r="L10" t="n">
-        <v>14.555555555555555</v>
+        <v>29.043478260869566</v>
       </c>
       <c r="M10" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.9110576923076923</v>
+        <v>1.8577075098814229</v>
       </c>
     </row>
     <row r="11">
@@ -838,40 +838,40 @@
         <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="D11" t="n">
-        <v>675.0</v>
+        <v>1030.0</v>
       </c>
       <c r="E11" t="n">
-        <v>39.705882352941174</v>
+        <v>44.78260869565217</v>
       </c>
       <c r="F11" t="n">
-        <v>7100.0</v>
+        <v>13450.0</v>
       </c>
       <c r="G11" t="n">
-        <v>417.6470588235294</v>
+        <v>584.7826086956521</v>
       </c>
       <c r="H11" t="n">
-        <v>3900.0</v>
+        <v>9400.0</v>
       </c>
       <c r="I11" t="n">
-        <v>229.41176470588235</v>
+        <v>408.69565217391306</v>
       </c>
       <c r="J11" t="n">
-        <v>13.823529411764707</v>
+        <v>41.30434782608695</v>
       </c>
       <c r="K11" t="n">
-        <v>16.41176470588235</v>
+        <v>38.82608695652174</v>
       </c>
       <c r="L11" t="n">
-        <v>10.941176470588236</v>
+        <v>35.47826086956522</v>
       </c>
       <c r="M11" t="n">
         <v>22.0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.790450928381963</v>
+        <v>2.0038910505836576</v>
       </c>
     </row>
     <row r="12">
@@ -882,40 +882,40 @@
         <v>72</v>
       </c>
       <c r="C12" t="n">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="D12" t="n">
-        <v>725.0</v>
+        <v>815.0</v>
       </c>
       <c r="E12" t="n">
-        <v>42.64705882352941</v>
+        <v>40.75</v>
       </c>
       <c r="F12" t="n">
-        <v>7950.0</v>
+        <v>8750.0</v>
       </c>
       <c r="G12" t="n">
-        <v>467.6470588235294</v>
+        <v>437.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4100.0</v>
+        <v>4800.0</v>
       </c>
       <c r="I12" t="n">
-        <v>241.1764705882353</v>
+        <v>240.0</v>
       </c>
       <c r="J12" t="n">
-        <v>30.529411764705884</v>
+        <v>53.55</v>
       </c>
       <c r="K12" t="n">
-        <v>24.058823529411764</v>
+        <v>44.55</v>
       </c>
       <c r="L12" t="n">
-        <v>21.705882352941178</v>
+        <v>46.9</v>
       </c>
       <c r="M12" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.821608040201005</v>
+        <v>1.6804123711340206</v>
       </c>
     </row>
     <row r="13">
@@ -926,40 +926,40 @@
         <v>73</v>
       </c>
       <c r="C13" t="n">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="D13" t="n">
-        <v>710.0</v>
+        <v>870.0</v>
       </c>
       <c r="E13" t="n">
-        <v>41.76470588235294</v>
+        <v>43.5</v>
       </c>
       <c r="F13" t="n">
-        <v>9100.0</v>
+        <v>8450.0</v>
       </c>
       <c r="G13" t="n">
-        <v>535.2941176470588</v>
+        <v>422.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5200.0</v>
+        <v>7550.0</v>
       </c>
       <c r="I13" t="n">
-        <v>305.88235294117646</v>
+        <v>377.5</v>
       </c>
       <c r="J13" t="n">
-        <v>11.411764705882353</v>
+        <v>32.55</v>
       </c>
       <c r="K13" t="n">
-        <v>11.411764705882353</v>
+        <v>48.15</v>
       </c>
       <c r="L13" t="n">
-        <v>11.411764705882353</v>
+        <v>38.05</v>
       </c>
       <c r="M13" t="n">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6099773242630386</v>
+        <v>1.9954128440366972</v>
       </c>
     </row>
     <row r="14">
@@ -970,40 +970,40 @@
         <v>74</v>
       </c>
       <c r="C14" t="n">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="D14" t="n">
-        <v>585.0</v>
+        <v>850.0</v>
       </c>
       <c r="E14" t="n">
-        <v>41.785714285714285</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="F14" t="n">
-        <v>6800.0</v>
+        <v>10350.0</v>
       </c>
       <c r="G14" t="n">
-        <v>485.7142857142857</v>
+        <v>544.7368421052631</v>
       </c>
       <c r="H14" t="n">
-        <v>3200.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I14" t="n">
-        <v>228.57142857142858</v>
+        <v>447.36842105263156</v>
       </c>
       <c r="J14" t="n">
-        <v>26.214285714285715</v>
+        <v>36.94736842105263</v>
       </c>
       <c r="K14" t="n">
-        <v>33.142857142857146</v>
+        <v>38.68421052631579</v>
       </c>
       <c r="L14" t="n">
-        <v>24.928571428571427</v>
+        <v>31.736842105263158</v>
       </c>
       <c r="M14" t="n">
         <v>22.0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8810289389067525</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
@@ -1014,40 +1014,40 @@
         <v>75</v>
       </c>
       <c r="C15" t="n">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="D15" t="n">
-        <v>560.0</v>
+        <v>590.0</v>
       </c>
       <c r="E15" t="n">
-        <v>40.0</v>
+        <v>32.77777777777778</v>
       </c>
       <c r="F15" t="n">
-        <v>5400.0</v>
+        <v>4600.0</v>
       </c>
       <c r="G15" t="n">
-        <v>385.7142857142857</v>
+        <v>255.55555555555554</v>
       </c>
       <c r="H15" t="n">
-        <v>4300.0</v>
+        <v>3300.0</v>
       </c>
       <c r="I15" t="n">
-        <v>307.14285714285717</v>
+        <v>183.33333333333334</v>
       </c>
       <c r="J15" t="n">
-        <v>24.214285714285715</v>
+        <v>36.611111111111114</v>
       </c>
       <c r="K15" t="n">
-        <v>31.642857142857142</v>
+        <v>57.72222222222222</v>
       </c>
       <c r="L15" t="n">
-        <v>24.214285714285715</v>
+        <v>43.111111111111114</v>
       </c>
       <c r="M15" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.0216606498194944</v>
+        <v>1.6298342541436464</v>
       </c>
     </row>
     <row r="16">
@@ -1058,40 +1058,40 @@
         <v>76</v>
       </c>
       <c r="C16" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="D16" t="n">
-        <v>415.0</v>
+        <v>685.0</v>
       </c>
       <c r="E16" t="n">
-        <v>31.923076923076923</v>
+        <v>40.294117647058826</v>
       </c>
       <c r="F16" t="n">
-        <v>2800.0</v>
+        <v>6850.0</v>
       </c>
       <c r="G16" t="n">
-        <v>215.3846153846154</v>
+        <v>402.94117647058823</v>
       </c>
       <c r="H16" t="n">
-        <v>1900.0</v>
+        <v>5000.0</v>
       </c>
       <c r="I16" t="n">
-        <v>146.15384615384616</v>
+        <v>294.11764705882354</v>
       </c>
       <c r="J16" t="n">
-        <v>24.846153846153847</v>
+        <v>41.470588235294116</v>
       </c>
       <c r="K16" t="n">
-        <v>26.615384615384617</v>
+        <v>41.294117647058826</v>
       </c>
       <c r="L16" t="n">
-        <v>23.0</v>
+        <v>42.8235294117647</v>
       </c>
       <c r="M16" t="n">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4716312056737588</v>
+        <v>1.9350282485875707</v>
       </c>
     </row>
     <row r="17">
@@ -1102,40 +1102,40 @@
         <v>77</v>
       </c>
       <c r="C17" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="D17" t="n">
-        <v>440.0</v>
+        <v>465.0</v>
       </c>
       <c r="E17" t="n">
-        <v>36.666666666666664</v>
+        <v>31.0</v>
       </c>
       <c r="F17" t="n">
-        <v>4500.0</v>
+        <v>3100.0</v>
       </c>
       <c r="G17" t="n">
-        <v>375.0</v>
+        <v>206.66666666666666</v>
       </c>
       <c r="H17" t="n">
-        <v>900.0</v>
+        <v>3700.0</v>
       </c>
       <c r="I17" t="n">
-        <v>75.0</v>
+        <v>246.66666666666666</v>
       </c>
       <c r="J17" t="n">
-        <v>24.75</v>
+        <v>37.06666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>22.833333333333332</v>
+        <v>34.6</v>
       </c>
       <c r="L17" t="n">
-        <v>17.25</v>
+        <v>32.53333333333333</v>
       </c>
       <c r="M17" t="n">
         <v>22.0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6666666666666667</v>
+        <v>1.404833836858006</v>
       </c>
     </row>
     <row r="18">
@@ -1146,40 +1146,40 @@
         <v>78</v>
       </c>
       <c r="C18" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="D18" t="n">
-        <v>490.0</v>
+        <v>605.0</v>
       </c>
       <c r="E18" t="n">
-        <v>40.833333333333336</v>
+        <v>40.333333333333336</v>
       </c>
       <c r="F18" t="n">
-        <v>4700.0</v>
+        <v>5400.0</v>
       </c>
       <c r="G18" t="n">
-        <v>391.6666666666667</v>
+        <v>360.0</v>
       </c>
       <c r="H18" t="n">
-        <v>2500.0</v>
+        <v>4850.0</v>
       </c>
       <c r="I18" t="n">
-        <v>208.33333333333334</v>
+        <v>323.3333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>13.916666666666666</v>
+        <v>30.8</v>
       </c>
       <c r="K18" t="n">
-        <v>21.0</v>
+        <v>48.733333333333334</v>
       </c>
       <c r="L18" t="n">
-        <v>13.0</v>
+        <v>39.46666666666667</v>
       </c>
       <c r="M18" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9291338582677164</v>
+        <v>2.037037037037037</v>
       </c>
     </row>
     <row r="19">
@@ -1190,40 +1190,40 @@
         <v>79</v>
       </c>
       <c r="C19" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="D19" t="n">
-        <v>390.0</v>
+        <v>700.0</v>
       </c>
       <c r="E19" t="n">
-        <v>32.5</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="F19" t="n">
-        <v>2900.0</v>
+        <v>9300.0</v>
       </c>
       <c r="G19" t="n">
-        <v>241.66666666666666</v>
+        <v>620.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1500.0</v>
+        <v>7300.0</v>
       </c>
       <c r="I19" t="n">
-        <v>125.0</v>
+        <v>486.6666666666667</v>
       </c>
       <c r="J19" t="n">
-        <v>19.583333333333332</v>
+        <v>45.46666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>36.833333333333336</v>
+        <v>44.93333333333333</v>
       </c>
       <c r="L19" t="n">
-        <v>26.916666666666668</v>
+        <v>29.6</v>
       </c>
       <c r="M19" t="n">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5918367346938775</v>
+        <v>1.9607843137254901</v>
       </c>
     </row>
     <row r="20">
@@ -1234,40 +1234,40 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="D20" t="n">
-        <v>605.0</v>
+        <v>730.0</v>
       </c>
       <c r="E20" t="n">
-        <v>50.416666666666664</v>
+        <v>52.142857142857146</v>
       </c>
       <c r="F20" t="n">
-        <v>8650.0</v>
+        <v>9250.0</v>
       </c>
       <c r="G20" t="n">
-        <v>720.8333333333334</v>
+        <v>660.7142857142857</v>
       </c>
       <c r="H20" t="n">
-        <v>4200.0</v>
+        <v>7200.0</v>
       </c>
       <c r="I20" t="n">
-        <v>350.0</v>
+        <v>514.2857142857143</v>
       </c>
       <c r="J20" t="n">
-        <v>29.833333333333332</v>
+        <v>46.57142857142857</v>
       </c>
       <c r="K20" t="n">
-        <v>39.666666666666664</v>
+        <v>49.07142857142857</v>
       </c>
       <c r="L20" t="n">
-        <v>24.083333333333332</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="M20" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1006944444444446</v>
+        <v>1.9676549865229112</v>
       </c>
     </row>
     <row r="21">
@@ -1278,40 +1278,40 @@
         <v>81</v>
       </c>
       <c r="C21" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="D21" t="n">
-        <v>475.0</v>
+        <v>580.0</v>
       </c>
       <c r="E21" t="n">
-        <v>47.5</v>
+        <v>41.42857142857143</v>
       </c>
       <c r="F21" t="n">
-        <v>5650.0</v>
+        <v>6000.0</v>
       </c>
       <c r="G21" t="n">
-        <v>565.0</v>
+        <v>428.57142857142856</v>
       </c>
       <c r="H21" t="n">
-        <v>2400.0</v>
+        <v>4900.0</v>
       </c>
       <c r="I21" t="n">
-        <v>240.0</v>
+        <v>350.0</v>
       </c>
       <c r="J21" t="n">
-        <v>23.8</v>
+        <v>31.357142857142858</v>
       </c>
       <c r="K21" t="n">
-        <v>33.2</v>
+        <v>49.285714285714285</v>
       </c>
       <c r="L21" t="n">
-        <v>23.0</v>
+        <v>34.0</v>
       </c>
       <c r="M21" t="n">
-        <v>24.0</v>
+        <v>21.0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9076305220883534</v>
+        <v>1.9463087248322148</v>
       </c>
     </row>
     <row r="22">
@@ -1322,40 +1322,40 @@
         <v>82</v>
       </c>
       <c r="C22" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="D22" t="n">
-        <v>290.0</v>
+        <v>485.0</v>
       </c>
       <c r="E22" t="n">
-        <v>29.0</v>
+        <v>40.416666666666664</v>
       </c>
       <c r="F22" t="n">
-        <v>1900.0</v>
+        <v>5050.0</v>
       </c>
       <c r="G22" t="n">
-        <v>190.0</v>
+        <v>420.8333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>1900.0</v>
+        <v>4300.0</v>
       </c>
       <c r="I22" t="n">
-        <v>190.0</v>
+        <v>358.3333333333333</v>
       </c>
       <c r="J22" t="n">
-        <v>54.2</v>
+        <v>41.583333333333336</v>
       </c>
       <c r="K22" t="n">
-        <v>19.0</v>
+        <v>32.083333333333336</v>
       </c>
       <c r="L22" t="n">
-        <v>36.1</v>
+        <v>31.75</v>
       </c>
       <c r="M22" t="n">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.355140186915888</v>
+        <v>1.4923076923076923</v>
       </c>
     </row>
     <row r="23">
@@ -1366,40 +1366,40 @@
         <v>83</v>
       </c>
       <c r="C23" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D23" t="n">
-        <v>330.0</v>
+        <v>290.0</v>
       </c>
       <c r="E23" t="n">
-        <v>41.25</v>
+        <v>29.0</v>
       </c>
       <c r="F23" t="n">
-        <v>3300.0</v>
+        <v>1900.0</v>
       </c>
       <c r="G23" t="n">
-        <v>412.5</v>
+        <v>190.0</v>
       </c>
       <c r="H23" t="n">
-        <v>600.0</v>
+        <v>1900.0</v>
       </c>
       <c r="I23" t="n">
-        <v>75.0</v>
+        <v>190.0</v>
       </c>
       <c r="J23" t="n">
-        <v>16.125</v>
+        <v>54.2</v>
       </c>
       <c r="K23" t="n">
-        <v>20.75</v>
+        <v>19.0</v>
       </c>
       <c r="L23" t="n">
-        <v>16.0</v>
+        <v>36.1</v>
       </c>
       <c r="M23" t="n">
         <v>21.0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.9642857142857142</v>
+        <v>1.355140186915888</v>
       </c>
     </row>
     <row r="24">
@@ -1410,40 +1410,40 @@
         <v>84</v>
       </c>
       <c r="C24" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="D24" t="n">
-        <v>235.0</v>
+        <v>390.0</v>
       </c>
       <c r="E24" t="n">
-        <v>39.166666666666664</v>
+        <v>39.0</v>
       </c>
       <c r="F24" t="n">
-        <v>1950.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G24" t="n">
-        <v>325.0</v>
+        <v>350.0</v>
       </c>
       <c r="H24" t="n">
-        <v>100.0</v>
+        <v>1800.0</v>
       </c>
       <c r="I24" t="n">
-        <v>16.666666666666668</v>
+        <v>180.0</v>
       </c>
       <c r="J24" t="n">
-        <v>6.0</v>
+        <v>35.6</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0</v>
+        <v>54.7</v>
       </c>
       <c r="L24" t="n">
-        <v>6.0</v>
+        <v>38.7</v>
       </c>
       <c r="M24" t="n">
-        <v>26.0</v>
+        <v>21.0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4968152866242037</v>
+        <v>1.8483412322274881</v>
       </c>
     </row>
     <row r="25">
@@ -1454,40 +1454,40 @@
         <v>85</v>
       </c>
       <c r="C25" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D25" t="n">
-        <v>175.0</v>
+        <v>290.0</v>
       </c>
       <c r="E25" t="n">
-        <v>35.0</v>
+        <v>36.25</v>
       </c>
       <c r="F25" t="n">
-        <v>1850.0</v>
+        <v>3600.0</v>
       </c>
       <c r="G25" t="n">
-        <v>370.0</v>
+        <v>450.0</v>
       </c>
       <c r="H25" t="n">
-        <v>300.0</v>
+        <v>3550.0</v>
       </c>
       <c r="I25" t="n">
-        <v>60.0</v>
+        <v>443.75</v>
       </c>
       <c r="J25" t="n">
-        <v>27.8</v>
+        <v>39.125</v>
       </c>
       <c r="K25" t="n">
-        <v>36.2</v>
+        <v>39.0</v>
       </c>
       <c r="L25" t="n">
-        <v>25.8</v>
+        <v>31.75</v>
       </c>
       <c r="M25" t="n">
-        <v>24.0</v>
+        <v>21.0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4462809917355373</v>
+        <v>1.7159763313609468</v>
       </c>
     </row>
     <row r="26">
@@ -1498,40 +1498,40 @@
         <v>86</v>
       </c>
       <c r="C26" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D26" t="n">
-        <v>200.0</v>
+        <v>350.0</v>
       </c>
       <c r="E26" t="n">
-        <v>40.0</v>
+        <v>43.75</v>
       </c>
       <c r="F26" t="n">
-        <v>2100.0</v>
+        <v>3900.0</v>
       </c>
       <c r="G26" t="n">
-        <v>420.0</v>
+        <v>487.5</v>
       </c>
       <c r="H26" t="n">
-        <v>1100.0</v>
+        <v>3800.0</v>
       </c>
       <c r="I26" t="n">
-        <v>220.0</v>
+        <v>475.0</v>
       </c>
       <c r="J26" t="n">
-        <v>37.0</v>
+        <v>47.75</v>
       </c>
       <c r="K26" t="n">
-        <v>22.4</v>
+        <v>33.0</v>
       </c>
       <c r="L26" t="n">
-        <v>22.4</v>
+        <v>30.875</v>
       </c>
       <c r="M26" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5151515151515151</v>
+        <v>1.7073170731707317</v>
       </c>
     </row>
     <row r="27">
@@ -1542,40 +1542,40 @@
         <v>87</v>
       </c>
       <c r="C27" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="D27" t="n">
-        <v>190.0</v>
+        <v>315.0</v>
       </c>
       <c r="E27" t="n">
-        <v>47.5</v>
+        <v>45.0</v>
       </c>
       <c r="F27" t="n">
-        <v>2100.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G27" t="n">
-        <v>525.0</v>
+        <v>500.0</v>
       </c>
       <c r="H27" t="n">
-        <v>300.0</v>
+        <v>2650.0</v>
       </c>
       <c r="I27" t="n">
-        <v>75.0</v>
+        <v>378.57142857142856</v>
       </c>
       <c r="J27" t="n">
-        <v>39.25</v>
+        <v>46.714285714285715</v>
       </c>
       <c r="K27" t="n">
-        <v>21.75</v>
+        <v>34.714285714285715</v>
       </c>
       <c r="L27" t="n">
-        <v>21.5</v>
+        <v>32.714285714285715</v>
       </c>
       <c r="M27" t="n">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.043010752688172</v>
+        <v>1.6935483870967742</v>
       </c>
     </row>
     <row r="28">
@@ -1586,40 +1586,40 @@
         <v>88</v>
       </c>
       <c r="C28" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="D28" t="n">
-        <v>230.0</v>
+        <v>350.0</v>
       </c>
       <c r="E28" t="n">
-        <v>57.5</v>
+        <v>50.0</v>
       </c>
       <c r="F28" t="n">
-        <v>3300.0</v>
+        <v>4950.0</v>
       </c>
       <c r="G28" t="n">
-        <v>825.0</v>
+        <v>707.1428571428571</v>
       </c>
       <c r="H28" t="n">
-        <v>2850.0</v>
+        <v>3600.0</v>
       </c>
       <c r="I28" t="n">
-        <v>712.5</v>
+        <v>514.2857142857143</v>
       </c>
       <c r="J28" t="n">
-        <v>21.0</v>
+        <v>43.42857142857143</v>
       </c>
       <c r="K28" t="n">
-        <v>25.5</v>
+        <v>41.57142857142857</v>
       </c>
       <c r="L28" t="n">
-        <v>21.0</v>
+        <v>27.857142857142858</v>
       </c>
       <c r="M28" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6436781609195403</v>
+        <v>2.095808383233533</v>
       </c>
     </row>
     <row r="29">
@@ -1630,40 +1630,40 @@
         <v>89</v>
       </c>
       <c r="C29" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D29" t="n">
-        <v>230.0</v>
+        <v>215.0</v>
       </c>
       <c r="E29" t="n">
-        <v>57.5</v>
+        <v>35.833333333333336</v>
       </c>
       <c r="F29" t="n">
-        <v>3100.0</v>
+        <v>2150.0</v>
       </c>
       <c r="G29" t="n">
-        <v>775.0</v>
+        <v>358.3333333333333</v>
       </c>
       <c r="H29" t="n">
-        <v>400.0</v>
+        <v>1800.0</v>
       </c>
       <c r="I29" t="n">
-        <v>100.0</v>
+        <v>300.0</v>
       </c>
       <c r="J29" t="n">
-        <v>11.25</v>
+        <v>35.0</v>
       </c>
       <c r="K29" t="n">
-        <v>12.5</v>
+        <v>47.666666666666664</v>
       </c>
       <c r="L29" t="n">
-        <v>11.25</v>
+        <v>38.666666666666664</v>
       </c>
       <c r="M29" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6436781609195403</v>
+        <v>1.4827586206896552</v>
       </c>
     </row>
     <row r="30">
@@ -1674,40 +1674,40 @@
         <v>90</v>
       </c>
       <c r="C30" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D30" t="n">
-        <v>120.0</v>
+        <v>290.0</v>
       </c>
       <c r="E30" t="n">
-        <v>30.0</v>
+        <v>48.333333333333336</v>
       </c>
       <c r="F30" t="n">
-        <v>1100.0</v>
+        <v>3300.0</v>
       </c>
       <c r="G30" t="n">
-        <v>275.0</v>
+        <v>550.0</v>
       </c>
       <c r="H30" t="n">
-        <v>900.0</v>
+        <v>1800.0</v>
       </c>
       <c r="I30" t="n">
-        <v>225.0</v>
+        <v>300.0</v>
       </c>
       <c r="J30" t="n">
-        <v>22.75</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>23.75</v>
+        <v>33.0</v>
       </c>
       <c r="L30" t="n">
-        <v>23.75</v>
+        <v>32.833333333333336</v>
       </c>
       <c r="M30" t="n">
         <v>24.0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.2244897959183674</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="31">
@@ -1718,40 +1718,40 @@
         <v>91</v>
       </c>
       <c r="C31" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D31" t="n">
-        <v>155.0</v>
+        <v>270.0</v>
       </c>
       <c r="E31" t="n">
-        <v>38.75</v>
+        <v>45.0</v>
       </c>
       <c r="F31" t="n">
-        <v>1100.0</v>
+        <v>3700.0</v>
       </c>
       <c r="G31" t="n">
-        <v>275.0</v>
+        <v>616.6666666666666</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0</v>
+        <v>3400.0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0</v>
+        <v>566.6666666666666</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0</v>
+        <v>31.666666666666668</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0</v>
+        <v>32.0</v>
       </c>
       <c r="M31" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.8235294117647058</v>
+        <v>1.9708029197080292</v>
       </c>
     </row>
     <row r="32">
@@ -1762,40 +1762,40 @@
         <v>92</v>
       </c>
       <c r="C32" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="D32" t="n">
-        <v>70.0</v>
+        <v>200.0</v>
       </c>
       <c r="E32" t="n">
-        <v>23.333333333333332</v>
+        <v>40.0</v>
       </c>
       <c r="F32" t="n">
-        <v>200.0</v>
+        <v>2800.0</v>
       </c>
       <c r="G32" t="n">
-        <v>66.66666666666667</v>
+        <v>560.0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0</v>
+        <v>2700.0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0</v>
+        <v>540.0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0</v>
+        <v>39.2</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0</v>
+        <v>26.6</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0</v>
+        <v>26.6</v>
       </c>
       <c r="M32" t="n">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.1666666666666667</v>
+        <v>1.639344262295082</v>
       </c>
     </row>
     <row r="33">
@@ -1806,40 +1806,40 @@
         <v>93</v>
       </c>
       <c r="C33" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="D33" t="n">
-        <v>150.0</v>
+        <v>220.0</v>
       </c>
       <c r="E33" t="n">
-        <v>50.0</v>
+        <v>44.0</v>
       </c>
       <c r="F33" t="n">
-        <v>1600.0</v>
+        <v>3100.0</v>
       </c>
       <c r="G33" t="n">
-        <v>533.3333333333334</v>
+        <v>620.0</v>
       </c>
       <c r="H33" t="n">
-        <v>1400.0</v>
+        <v>2600.0</v>
       </c>
       <c r="I33" t="n">
-        <v>466.6666666666667</v>
+        <v>520.0</v>
       </c>
       <c r="J33" t="n">
-        <v>40.0</v>
+        <v>42.6</v>
       </c>
       <c r="K33" t="n">
-        <v>30.0</v>
+        <v>50.2</v>
       </c>
       <c r="L33" t="n">
-        <v>26.333333333333332</v>
+        <v>54.8</v>
       </c>
       <c r="M33" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3076923076923075</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="34">
@@ -1850,40 +1850,40 @@
         <v>94</v>
       </c>
       <c r="C34" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D34" t="n">
-        <v>205.0</v>
+        <v>120.0</v>
       </c>
       <c r="E34" t="n">
-        <v>68.33333333333333</v>
+        <v>30.0</v>
       </c>
       <c r="F34" t="n">
-        <v>3800.0</v>
+        <v>800.0</v>
       </c>
       <c r="G34" t="n">
-        <v>1266.6666666666667</v>
+        <v>200.0</v>
       </c>
       <c r="H34" t="n">
-        <v>2700.0</v>
+        <v>800.0</v>
       </c>
       <c r="I34" t="n">
-        <v>900.0</v>
+        <v>200.0</v>
       </c>
       <c r="J34" t="n">
-        <v>24.333333333333332</v>
+        <v>38.75</v>
       </c>
       <c r="K34" t="n">
-        <v>15.333333333333334</v>
+        <v>53.5</v>
       </c>
       <c r="L34" t="n">
-        <v>15.333333333333334</v>
+        <v>40.0</v>
       </c>
       <c r="M34" t="n">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6973684210526314</v>
+        <v>1.3793103448275863</v>
       </c>
     </row>
     <row r="35">
@@ -1894,40 +1894,40 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D35" t="n">
-        <v>160.0</v>
+        <v>230.0</v>
       </c>
       <c r="E35" t="n">
-        <v>53.333333333333336</v>
+        <v>57.5</v>
       </c>
       <c r="F35" t="n">
-        <v>2400.0</v>
+        <v>3100.0</v>
       </c>
       <c r="G35" t="n">
-        <v>800.0</v>
+        <v>775.0</v>
       </c>
       <c r="H35" t="n">
-        <v>100.0</v>
+        <v>1650.0</v>
       </c>
       <c r="I35" t="n">
-        <v>33.333333333333336</v>
+        <v>412.5</v>
       </c>
       <c r="J35" t="n">
-        <v>12.333333333333334</v>
+        <v>48.75</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0</v>
+        <v>40.25</v>
       </c>
       <c r="L35" t="n">
-        <v>12.333333333333334</v>
+        <v>48.75</v>
       </c>
       <c r="M35" t="n">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2535211267605635</v>
+        <v>2.6436781609195403</v>
       </c>
     </row>
     <row r="36">
@@ -1938,40 +1938,40 @@
         <v>96</v>
       </c>
       <c r="C36" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D36" t="n">
-        <v>50.0</v>
+        <v>120.0</v>
       </c>
       <c r="E36" t="n">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="F36" t="n">
-        <v>400.0</v>
+        <v>1100.0</v>
       </c>
       <c r="G36" t="n">
-        <v>200.0</v>
+        <v>275.0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0</v>
+        <v>900.0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0</v>
+        <v>225.0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0</v>
+        <v>44.0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0</v>
+        <v>23.75</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0</v>
+        <v>45.0</v>
       </c>
       <c r="M36" t="n">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.2195121951219512</v>
+        <v>1.2244897959183674</v>
       </c>
     </row>
     <row r="37">
@@ -1982,40 +1982,40 @@
         <v>97</v>
       </c>
       <c r="C37" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D37" t="n">
-        <v>90.0</v>
+        <v>150.0</v>
       </c>
       <c r="E37" t="n">
-        <v>45.0</v>
+        <v>50.0</v>
       </c>
       <c r="F37" t="n">
-        <v>900.0</v>
+        <v>1600.0</v>
       </c>
       <c r="G37" t="n">
-        <v>450.0</v>
+        <v>533.3333333333334</v>
       </c>
       <c r="H37" t="n">
-        <v>400.0</v>
+        <v>1400.0</v>
       </c>
       <c r="I37" t="n">
-        <v>200.0</v>
+        <v>466.6666666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>19.0</v>
+        <v>40.0</v>
       </c>
       <c r="K37" t="n">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="L37" t="n">
-        <v>19.0</v>
+        <v>26.333333333333332</v>
       </c>
       <c r="M37" t="n">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.7647058823529411</v>
+        <v>2.3076923076923075</v>
       </c>
     </row>
     <row r="38">
@@ -2026,40 +2026,40 @@
         <v>98</v>
       </c>
       <c r="C38" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D38" t="n">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="E38" t="n">
-        <v>40.0</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="F38" t="n">
-        <v>600.0</v>
+        <v>400.0</v>
       </c>
       <c r="G38" t="n">
-        <v>300.0</v>
+        <v>133.33333333333334</v>
       </c>
       <c r="H38" t="n">
-        <v>600.0</v>
+        <v>800.0</v>
       </c>
       <c r="I38" t="n">
-        <v>300.0</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="J38" t="n">
-        <v>23.5</v>
+        <v>35.333333333333336</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>37.666666666666664</v>
       </c>
       <c r="L38" t="n">
-        <v>3.5</v>
+        <v>34.666666666666664</v>
       </c>
       <c r="M38" t="n">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3529411764705883</v>
+        <v>1.408450704225352</v>
       </c>
     </row>
     <row r="39">
@@ -2070,40 +2070,40 @@
         <v>99</v>
       </c>
       <c r="C39" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D39" t="n">
-        <v>110.0</v>
+        <v>160.0</v>
       </c>
       <c r="E39" t="n">
-        <v>55.0</v>
+        <v>53.333333333333336</v>
       </c>
       <c r="F39" t="n">
-        <v>1800.0</v>
+        <v>2400.0</v>
       </c>
       <c r="G39" t="n">
-        <v>900.0</v>
+        <v>800.0</v>
       </c>
       <c r="H39" t="n">
-        <v>700.0</v>
+        <v>2500.0</v>
       </c>
       <c r="I39" t="n">
-        <v>350.0</v>
+        <v>833.3333333333334</v>
       </c>
       <c r="J39" t="n">
-        <v>27.5</v>
+        <v>36.0</v>
       </c>
       <c r="K39" t="n">
-        <v>38.5</v>
+        <v>32.0</v>
       </c>
       <c r="L39" t="n">
-        <v>27.5</v>
+        <v>36.0</v>
       </c>
       <c r="M39" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.2535211267605635</v>
       </c>
     </row>
     <row r="40">
@@ -2114,40 +2114,40 @@
         <v>100</v>
       </c>
       <c r="C40" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D40" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="E40" t="n">
         <v>40.0</v>
       </c>
-      <c r="E40" t="n">
-        <v>20.0</v>
-      </c>
       <c r="F40" t="n">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0</v>
+        <v>433.3333333333333</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0</v>
+        <v>46.333333333333336</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0</v>
+        <v>32.333333333333336</v>
       </c>
       <c r="M40" t="n">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.0</v>
+        <v>1.4457831325301205</v>
       </c>
     </row>
     <row r="41">
@@ -2158,40 +2158,40 @@
         <v>101</v>
       </c>
       <c r="C41" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D41" t="n">
-        <v>100.0</v>
+        <v>130.0</v>
       </c>
       <c r="E41" t="n">
-        <v>50.0</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="F41" t="n">
-        <v>800.0</v>
+        <v>2100.0</v>
       </c>
       <c r="G41" t="n">
-        <v>400.0</v>
+        <v>700.0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0</v>
+        <v>1400.0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0</v>
+        <v>466.6666666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="M41" t="n">
-        <v>32.0</v>
+        <v>23.0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.5384615384615385</v>
+        <v>1.8309859154929577</v>
       </c>
     </row>
     <row r="42">
@@ -2205,37 +2205,37 @@
         <v>2.0</v>
       </c>
       <c r="D42" t="n">
-        <v>75.0</v>
+        <v>90.0</v>
       </c>
       <c r="E42" t="n">
-        <v>37.5</v>
+        <v>45.0</v>
       </c>
       <c r="F42" t="n">
-        <v>1350.0</v>
+        <v>900.0</v>
       </c>
       <c r="G42" t="n">
-        <v>675.0</v>
+        <v>450.0</v>
       </c>
       <c r="H42" t="n">
-        <v>1100.0</v>
+        <v>400.0</v>
       </c>
       <c r="I42" t="n">
-        <v>550.0</v>
+        <v>200.0</v>
       </c>
       <c r="J42" t="n">
-        <v>4.5</v>
+        <v>42.0</v>
       </c>
       <c r="K42" t="n">
-        <v>17.5</v>
+        <v>68.5</v>
       </c>
       <c r="L42" t="n">
-        <v>4.5</v>
+        <v>42.0</v>
       </c>
       <c r="M42" t="n">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.829268292682927</v>
+        <v>1.7647058823529411</v>
       </c>
     </row>
     <row r="43">
@@ -2246,40 +2246,40 @@
         <v>103</v>
       </c>
       <c r="C43" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D43" t="n">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
       <c r="E43" t="n">
-        <v>75.0</v>
+        <v>40.0</v>
       </c>
       <c r="F43" t="n">
-        <v>1350.0</v>
+        <v>600.0</v>
       </c>
       <c r="G43" t="n">
-        <v>1350.0</v>
+        <v>300.0</v>
       </c>
       <c r="H43" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="I43" t="n">
-        <v>800.0</v>
+        <v>300.0</v>
       </c>
       <c r="J43" t="n">
-        <v>40.0</v>
+        <v>52.5</v>
       </c>
       <c r="K43" t="n">
-        <v>9.0</v>
+        <v>32.5</v>
       </c>
       <c r="L43" t="n">
-        <v>9.0</v>
+        <v>32.5</v>
       </c>
       <c r="M43" t="n">
-        <v>32.0</v>
+        <v>17.0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.34375</v>
+        <v>2.3529411764705883</v>
       </c>
     </row>
     <row r="44">
@@ -2290,40 +2290,40 @@
         <v>104</v>
       </c>
       <c r="C44" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D44" t="n">
-        <v>65.0</v>
+        <v>110.0</v>
       </c>
       <c r="E44" t="n">
-        <v>65.0</v>
+        <v>55.0</v>
       </c>
       <c r="F44" t="n">
-        <v>900.0</v>
+        <v>1800.0</v>
       </c>
       <c r="G44" t="n">
         <v>900.0</v>
       </c>
       <c r="H44" t="n">
-        <v>800.0</v>
+        <v>700.0</v>
       </c>
       <c r="I44" t="n">
-        <v>800.0</v>
+        <v>350.0</v>
       </c>
       <c r="J44" t="n">
-        <v>48.0</v>
+        <v>27.5</v>
       </c>
       <c r="K44" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="M44" t="n">
         <v>22.0</v>
       </c>
-      <c r="L44" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>29.0</v>
-      </c>
       <c r="N44" t="n">
-        <v>2.2413793103448274</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="45">
@@ -2337,37 +2337,37 @@
         <v>1.0</v>
       </c>
       <c r="D45" t="n">
-        <v>70.0</v>
+        <v>75.0</v>
       </c>
       <c r="E45" t="n">
-        <v>70.0</v>
+        <v>75.0</v>
       </c>
       <c r="F45" t="n">
-        <v>1200.0</v>
+        <v>1350.0</v>
       </c>
       <c r="G45" t="n">
-        <v>1200.0</v>
+        <v>1350.0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="M45" t="n">
-        <v>22.0</v>
+        <v>32.0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1818181818181817</v>
+        <v>2.34375</v>
       </c>
     </row>
     <row r="46">
@@ -2381,37 +2381,37 @@
         <v>1.0</v>
       </c>
       <c r="D46" t="n">
-        <v>20.0</v>
+        <v>65.0</v>
       </c>
       <c r="E46" t="n">
-        <v>20.0</v>
+        <v>65.0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0</v>
+        <v>900.0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0</v>
+        <v>900.0</v>
       </c>
       <c r="H46" t="n">
-        <v>100.0</v>
+        <v>800.0</v>
       </c>
       <c r="I46" t="n">
-        <v>100.0</v>
+        <v>800.0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0</v>
+        <v>48.0</v>
       </c>
       <c r="K46" t="n">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="L46" t="n">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="M46" t="n">
-        <v>16.0</v>
+        <v>29.0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.25</v>
+        <v>2.2413793103448274</v>
       </c>
     </row>
     <row r="47">
@@ -2425,37 +2425,37 @@
         <v>1.0</v>
       </c>
       <c r="D47" t="n">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
       <c r="E47" t="n">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
       <c r="F47" t="n">
-        <v>2000.0</v>
+        <v>1200.0</v>
       </c>
       <c r="G47" t="n">
-        <v>2000.0</v>
+        <v>1200.0</v>
       </c>
       <c r="H47" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="I47" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="J47" t="n">
-        <v>36.0</v>
+        <v>50.0</v>
       </c>
       <c r="K47" t="n">
-        <v>68.0</v>
+        <v>21.0</v>
       </c>
       <c r="L47" t="n">
-        <v>36.0</v>
+        <v>21.0</v>
       </c>
       <c r="M47" t="n">
-        <v>26.0</v>
+        <v>22.0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4615384615384617</v>
+        <v>3.1818181818181817</v>
       </c>
     </row>
     <row r="48">
@@ -2469,37 +2469,37 @@
         <v>1.0</v>
       </c>
       <c r="D48" t="n">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="E48" t="n">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="F48" t="n">
-        <v>400.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>400.0</v>
+        <v>0.0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="J48" t="n">
         <v>0.0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="M48" t="n">
-        <v>33.0</v>
+        <v>16.0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.5151515151515151</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="49">
@@ -2513,37 +2513,37 @@
         <v>1.0</v>
       </c>
       <c r="D49" t="n">
-        <v>40.0</v>
+        <v>90.0</v>
       </c>
       <c r="E49" t="n">
-        <v>40.0</v>
+        <v>90.0</v>
       </c>
       <c r="F49" t="n">
-        <v>300.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G49" t="n">
-        <v>300.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0</v>
+        <v>68.0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="M49" t="n">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.4814814814814814</v>
+        <v>3.4615384615384617</v>
       </c>
     </row>
     <row r="50">
@@ -2557,37 +2557,37 @@
         <v>1.0</v>
       </c>
       <c r="D50" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="E50" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="M50" t="n">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.3448275862068966</v>
+        <v>1.5151515151515151</v>
       </c>
     </row>
   </sheetData>

--- a/E1_refereestats.xlsx
+++ b/E1_refereestats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>Referee</t>
   </si>
@@ -197,9 +197,6 @@
     <t>48</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
     <t>Oliver Langford</t>
   </si>
   <si>
@@ -218,27 +215,27 @@
     <t>Gavin Ward</t>
   </si>
   <si>
+    <t>Samuel Allison</t>
+  </si>
+  <si>
     <t>Dean Whitestone</t>
   </si>
   <si>
+    <t>James Bell</t>
+  </si>
+  <si>
     <t>Matt Donohue</t>
   </si>
   <si>
-    <t>Samuel Allison</t>
-  </si>
-  <si>
-    <t>James Bell</t>
+    <t>Joshua Smith</t>
+  </si>
+  <si>
+    <t>Robert Madley</t>
   </si>
   <si>
     <t>Tom Nield</t>
   </si>
   <si>
-    <t>Joshua Smith</t>
-  </si>
-  <si>
-    <t>Robert Madley</t>
-  </si>
-  <si>
     <t>Andrew Davies</t>
   </si>
   <si>
@@ -251,21 +248,18 @@
     <t>Anthony Backhouse</t>
   </si>
   <si>
+    <t>Will Finnie</t>
+  </si>
+  <si>
     <t>Leigh Doughty</t>
   </si>
   <si>
     <t>Ben Toner</t>
   </si>
   <si>
-    <t>Will Finnie</t>
-  </si>
-  <si>
     <t>Farai Hallam</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Thomas Bramall</t>
   </si>
   <si>
@@ -305,21 +299,24 @@
     <t>Sunny Gill</t>
   </si>
   <si>
+    <t>Stuart Attwell</t>
+  </si>
+  <si>
     <t>Simon Hooper</t>
   </si>
   <si>
     <t>Ben Speedie</t>
   </si>
   <si>
-    <t>Stuart Attwell</t>
-  </si>
-  <si>
     <t>Robert Jones</t>
   </si>
   <si>
     <t>Craig Pawson</t>
   </si>
   <si>
+    <t>Keith Stroud</t>
+  </si>
+  <si>
     <t>Andy Madley</t>
   </si>
   <si>
@@ -330,9 +327,6 @@
   </si>
   <si>
     <t>Steve Martin</t>
-  </si>
-  <si>
-    <t>Keith Stroud</t>
   </si>
   <si>
     <t>Martin Coy</t>
@@ -439,43 +433,43 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="D2" t="n">
-        <v>1045.0</v>
+        <v>1075.0</v>
       </c>
       <c r="E2" t="n">
-        <v>38.7037037037037</v>
+        <v>38.392857142857146</v>
       </c>
       <c r="F2" t="n">
-        <v>12625.0</v>
+        <v>12825.0</v>
       </c>
       <c r="G2" t="n">
-        <v>467.5925925925926</v>
+        <v>458.0357142857143</v>
       </c>
       <c r="H2" t="n">
-        <v>11925.0</v>
+        <v>12125.0</v>
       </c>
       <c r="I2" t="n">
-        <v>441.6666666666667</v>
+        <v>433.0357142857143</v>
       </c>
       <c r="J2" t="n">
-        <v>47.370370370370374</v>
+        <v>47.82142857142857</v>
       </c>
       <c r="K2" t="n">
-        <v>36.7037037037037</v>
+        <v>36.42857142857143</v>
       </c>
       <c r="L2" t="n">
-        <v>39.81481481481482</v>
+        <v>39.42857142857143</v>
       </c>
       <c r="M2" t="n">
         <v>22.0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.71875</v>
+        <v>1.7145135566188199</v>
       </c>
     </row>
     <row r="3">
@@ -483,43 +477,43 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="D3" t="n">
-        <v>735.0</v>
+        <v>745.0</v>
       </c>
       <c r="E3" t="n">
-        <v>28.26923076923077</v>
+        <v>27.59259259259259</v>
       </c>
       <c r="F3" t="n">
         <v>5250.0</v>
       </c>
       <c r="G3" t="n">
-        <v>201.92307692307693</v>
+        <v>194.44444444444446</v>
       </c>
       <c r="H3" t="n">
         <v>3700.0</v>
       </c>
       <c r="I3" t="n">
-        <v>142.30769230769232</v>
+        <v>137.03703703703704</v>
       </c>
       <c r="J3" t="n">
-        <v>36.30769230769231</v>
+        <v>38.407407407407405</v>
       </c>
       <c r="K3" t="n">
-        <v>45.84615384615385</v>
+        <v>44.148148148148145</v>
       </c>
       <c r="L3" t="n">
-        <v>39.76923076923077</v>
+        <v>41.74074074074074</v>
       </c>
       <c r="M3" t="n">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3339382940108893</v>
+        <v>1.3185840707964602</v>
       </c>
     </row>
     <row r="4">
@@ -527,43 +521,43 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="D4" t="n">
-        <v>810.0</v>
+        <v>880.0</v>
       </c>
       <c r="E4" t="n">
-        <v>32.4</v>
+        <v>32.592592592592595</v>
       </c>
       <c r="F4" t="n">
-        <v>6050.0</v>
+        <v>6650.0</v>
       </c>
       <c r="G4" t="n">
-        <v>242.0</v>
+        <v>246.2962962962963</v>
       </c>
       <c r="H4" t="n">
-        <v>5100.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I4" t="n">
-        <v>204.0</v>
+        <v>203.7037037037037</v>
       </c>
       <c r="J4" t="n">
-        <v>41.32</v>
+        <v>40.2962962962963</v>
       </c>
       <c r="K4" t="n">
-        <v>35.88</v>
+        <v>33.96296296296296</v>
       </c>
       <c r="L4" t="n">
-        <v>42.64</v>
+        <v>40.22222222222222</v>
       </c>
       <c r="M4" t="n">
         <v>21.0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.542857142857143</v>
+        <v>1.5277777777777777</v>
       </c>
     </row>
     <row r="5">
@@ -571,43 +565,43 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>885.0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>34.03846153846154</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10150.0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>390.38461538461536</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6300.0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>242.30769230769232</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.80769230769231</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40.69230769230769</v>
+      </c>
+      <c r="L5" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="M5" t="n">
         <v>24.0</v>
       </c>
-      <c r="D5" t="n">
-        <v>835.0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>34.791666666666664</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9850.0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>410.4166666666667</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6000.0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>42.166666666666664</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47.208333333333336</v>
-      </c>
-      <c r="M5" t="n">
-        <v>25.0</v>
-      </c>
       <c r="N5" t="n">
-        <v>1.3733552631578947</v>
+        <v>1.3678516228748068</v>
       </c>
     </row>
     <row r="6">
@@ -615,43 +609,43 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="D6" t="n">
-        <v>945.0</v>
+        <v>955.0</v>
       </c>
       <c r="E6" t="n">
-        <v>39.375</v>
+        <v>38.2</v>
       </c>
       <c r="F6" t="n">
         <v>11550.0</v>
       </c>
       <c r="G6" t="n">
-        <v>481.25</v>
+        <v>462.0</v>
       </c>
       <c r="H6" t="n">
         <v>11500.0</v>
       </c>
       <c r="I6" t="n">
-        <v>479.1666666666667</v>
+        <v>460.0</v>
       </c>
       <c r="J6" t="n">
-        <v>29.5</v>
+        <v>28.32</v>
       </c>
       <c r="K6" t="n">
-        <v>30.375</v>
+        <v>31.76</v>
       </c>
       <c r="L6" t="n">
-        <v>30.916666666666668</v>
+        <v>32.28</v>
       </c>
       <c r="M6" t="n">
         <v>25.0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.575</v>
+        <v>1.5231259968102073</v>
       </c>
     </row>
     <row r="7">
@@ -659,43 +653,43 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1045.0</v>
+        <v>1075.0</v>
       </c>
       <c r="E7" t="n">
-        <v>43.541666666666664</v>
+        <v>43.0</v>
       </c>
       <c r="F7" t="n">
-        <v>12775.0</v>
+        <v>12975.0</v>
       </c>
       <c r="G7" t="n">
-        <v>532.2916666666666</v>
+        <v>519.0</v>
       </c>
       <c r="H7" t="n">
-        <v>8950.0</v>
+        <v>9150.0</v>
       </c>
       <c r="I7" t="n">
-        <v>372.9166666666667</v>
+        <v>366.0</v>
       </c>
       <c r="J7" t="n">
-        <v>44.166666666666664</v>
+        <v>45.16</v>
       </c>
       <c r="K7" t="n">
-        <v>47.833333333333336</v>
+        <v>46.04</v>
       </c>
       <c r="L7" t="n">
-        <v>35.916666666666664</v>
+        <v>34.6</v>
       </c>
       <c r="M7" t="n">
         <v>22.0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.9569288389513109</v>
+        <v>1.9545454545454546</v>
       </c>
     </row>
     <row r="8">
@@ -703,43 +697,43 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
         <v>24.0</v>
       </c>
       <c r="D8" t="n">
-        <v>835.0</v>
+        <v>990.0</v>
       </c>
       <c r="E8" t="n">
-        <v>34.791666666666664</v>
+        <v>41.25</v>
       </c>
       <c r="F8" t="n">
-        <v>8400.0</v>
+        <v>10900.0</v>
       </c>
       <c r="G8" t="n">
-        <v>350.0</v>
+        <v>454.1666666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>7500.0</v>
+        <v>9400.0</v>
       </c>
       <c r="I8" t="n">
-        <v>312.5</v>
+        <v>391.6666666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>37.625</v>
+        <v>33.625</v>
       </c>
       <c r="K8" t="n">
-        <v>44.041666666666664</v>
+        <v>38.916666666666664</v>
       </c>
       <c r="L8" t="n">
-        <v>42.125</v>
+        <v>28.416666666666668</v>
       </c>
       <c r="M8" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5099457504520795</v>
+        <v>1.8609022556390977</v>
       </c>
     </row>
     <row r="9">
@@ -747,43 +741,43 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
         <v>24.0</v>
       </c>
       <c r="D9" t="n">
-        <v>1085.0</v>
+        <v>835.0</v>
       </c>
       <c r="E9" t="n">
-        <v>45.208333333333336</v>
+        <v>34.791666666666664</v>
       </c>
       <c r="F9" t="n">
-        <v>13925.0</v>
+        <v>8400.0</v>
       </c>
       <c r="G9" t="n">
-        <v>580.2083333333334</v>
+        <v>350.0</v>
       </c>
       <c r="H9" t="n">
-        <v>9675.0</v>
+        <v>7500.0</v>
       </c>
       <c r="I9" t="n">
-        <v>403.125</v>
+        <v>312.5</v>
       </c>
       <c r="J9" t="n">
-        <v>35.208333333333336</v>
+        <v>37.625</v>
       </c>
       <c r="K9" t="n">
-        <v>43.041666666666664</v>
+        <v>44.041666666666664</v>
       </c>
       <c r="L9" t="n">
-        <v>34.375</v>
+        <v>42.125</v>
       </c>
       <c r="M9" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.0018450184501844</v>
+        <v>1.5099457504520795</v>
       </c>
     </row>
     <row r="10">
@@ -791,43 +785,43 @@
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="D10" t="n">
-        <v>940.0</v>
+        <v>1050.0</v>
       </c>
       <c r="E10" t="n">
-        <v>40.869565217391305</v>
+        <v>43.75</v>
       </c>
       <c r="F10" t="n">
-        <v>10500.0</v>
+        <v>13450.0</v>
       </c>
       <c r="G10" t="n">
-        <v>456.5217391304348</v>
+        <v>560.4166666666666</v>
       </c>
       <c r="H10" t="n">
-        <v>8800.0</v>
+        <v>9400.0</v>
       </c>
       <c r="I10" t="n">
-        <v>382.60869565217394</v>
+        <v>391.6666666666667</v>
       </c>
       <c r="J10" t="n">
-        <v>33.391304347826086</v>
+        <v>39.583333333333336</v>
       </c>
       <c r="K10" t="n">
-        <v>40.0</v>
+        <v>39.208333333333336</v>
       </c>
       <c r="L10" t="n">
-        <v>29.043478260869566</v>
+        <v>36.0</v>
       </c>
       <c r="M10" t="n">
         <v>22.0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.8577075098814229</v>
+        <v>1.9736842105263157</v>
       </c>
     </row>
     <row r="11">
@@ -835,43 +829,43 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="D11" t="n">
-        <v>1030.0</v>
+        <v>1085.0</v>
       </c>
       <c r="E11" t="n">
-        <v>44.78260869565217</v>
+        <v>45.208333333333336</v>
       </c>
       <c r="F11" t="n">
-        <v>13450.0</v>
+        <v>13925.0</v>
       </c>
       <c r="G11" t="n">
-        <v>584.7826086956521</v>
+        <v>580.2083333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>9400.0</v>
+        <v>9675.0</v>
       </c>
       <c r="I11" t="n">
-        <v>408.69565217391306</v>
+        <v>403.125</v>
       </c>
       <c r="J11" t="n">
-        <v>41.30434782608695</v>
+        <v>35.208333333333336</v>
       </c>
       <c r="K11" t="n">
-        <v>38.82608695652174</v>
+        <v>43.041666666666664</v>
       </c>
       <c r="L11" t="n">
-        <v>35.47826086956522</v>
+        <v>34.375</v>
       </c>
       <c r="M11" t="n">
         <v>22.0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.0038910505836576</v>
+        <v>2.0018450184501844</v>
       </c>
     </row>
     <row r="12">
@@ -879,43 +873,43 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="D12" t="n">
-        <v>815.0</v>
+        <v>910.0</v>
       </c>
       <c r="E12" t="n">
-        <v>40.75</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="F12" t="n">
         <v>8750.0</v>
       </c>
       <c r="G12" t="n">
-        <v>437.5</v>
+        <v>416.6666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>4800.0</v>
+        <v>7850.0</v>
       </c>
       <c r="I12" t="n">
-        <v>240.0</v>
+        <v>373.8095238095238</v>
       </c>
       <c r="J12" t="n">
-        <v>53.55</v>
+        <v>35.142857142857146</v>
       </c>
       <c r="K12" t="n">
-        <v>44.55</v>
+        <v>46.38095238095238</v>
       </c>
       <c r="L12" t="n">
-        <v>46.9</v>
+        <v>36.76190476190476</v>
       </c>
       <c r="M12" t="n">
-        <v>24.0</v>
+        <v>21.0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.6804123711340206</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="13">
@@ -923,43 +917,43 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" t="n">
         <v>20.0</v>
       </c>
       <c r="D13" t="n">
-        <v>870.0</v>
+        <v>860.0</v>
       </c>
       <c r="E13" t="n">
-        <v>43.5</v>
+        <v>43.0</v>
       </c>
       <c r="F13" t="n">
-        <v>8450.0</v>
+        <v>10350.0</v>
       </c>
       <c r="G13" t="n">
-        <v>422.5</v>
+        <v>517.5</v>
       </c>
       <c r="H13" t="n">
-        <v>7550.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I13" t="n">
-        <v>377.5</v>
+        <v>425.0</v>
       </c>
       <c r="J13" t="n">
-        <v>32.55</v>
+        <v>39.1</v>
       </c>
       <c r="K13" t="n">
-        <v>48.15</v>
+        <v>36.75</v>
       </c>
       <c r="L13" t="n">
-        <v>38.05</v>
+        <v>34.15</v>
       </c>
       <c r="M13" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9954128440366972</v>
+        <v>1.9111111111111112</v>
       </c>
     </row>
     <row r="14">
@@ -967,43 +961,43 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D14" t="n">
-        <v>850.0</v>
+        <v>815.0</v>
       </c>
       <c r="E14" t="n">
-        <v>44.73684210526316</v>
+        <v>40.75</v>
       </c>
       <c r="F14" t="n">
-        <v>10350.0</v>
+        <v>8750.0</v>
       </c>
       <c r="G14" t="n">
-        <v>544.7368421052631</v>
+        <v>437.5</v>
       </c>
       <c r="H14" t="n">
-        <v>8500.0</v>
+        <v>4800.0</v>
       </c>
       <c r="I14" t="n">
-        <v>447.36842105263156</v>
+        <v>240.0</v>
       </c>
       <c r="J14" t="n">
-        <v>36.94736842105263</v>
+        <v>53.55</v>
       </c>
       <c r="K14" t="n">
-        <v>38.68421052631579</v>
+        <v>44.55</v>
       </c>
       <c r="L14" t="n">
-        <v>31.736842105263158</v>
+        <v>46.9</v>
       </c>
       <c r="M14" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.0</v>
+        <v>1.6804123711340206</v>
       </c>
     </row>
     <row r="15">
@@ -1011,43 +1005,43 @@
         <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="D15" t="n">
-        <v>590.0</v>
+        <v>610.0</v>
       </c>
       <c r="E15" t="n">
-        <v>32.77777777777778</v>
+        <v>32.10526315789474</v>
       </c>
       <c r="F15" t="n">
         <v>4600.0</v>
       </c>
       <c r="G15" t="n">
-        <v>255.55555555555554</v>
+        <v>242.10526315789474</v>
       </c>
       <c r="H15" t="n">
         <v>3300.0</v>
       </c>
       <c r="I15" t="n">
-        <v>183.33333333333334</v>
+        <v>173.68421052631578</v>
       </c>
       <c r="J15" t="n">
-        <v>36.611111111111114</v>
+        <v>34.68421052631579</v>
       </c>
       <c r="K15" t="n">
-        <v>57.72222222222222</v>
+        <v>57.36842105263158</v>
       </c>
       <c r="L15" t="n">
-        <v>43.111111111111114</v>
+        <v>43.526315789473685</v>
       </c>
       <c r="M15" t="n">
         <v>20.0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6298342541436464</v>
+        <v>1.605263157894737</v>
       </c>
     </row>
     <row r="16">
@@ -1055,43 +1049,43 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="D16" t="n">
-        <v>685.0</v>
+        <v>745.0</v>
       </c>
       <c r="E16" t="n">
-        <v>40.294117647058826</v>
+        <v>41.388888888888886</v>
       </c>
       <c r="F16" t="n">
-        <v>6850.0</v>
+        <v>7650.0</v>
       </c>
       <c r="G16" t="n">
-        <v>402.94117647058823</v>
+        <v>425.0</v>
       </c>
       <c r="H16" t="n">
-        <v>5000.0</v>
+        <v>5800.0</v>
       </c>
       <c r="I16" t="n">
-        <v>294.11764705882354</v>
+        <v>322.22222222222223</v>
       </c>
       <c r="J16" t="n">
-        <v>41.470588235294116</v>
+        <v>44.22222222222222</v>
       </c>
       <c r="K16" t="n">
-        <v>41.294117647058826</v>
+        <v>40.22222222222222</v>
       </c>
       <c r="L16" t="n">
-        <v>42.8235294117647</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="M16" t="n">
         <v>20.0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9350282485875707</v>
+        <v>2.0135135135135136</v>
       </c>
     </row>
     <row r="17">
@@ -1099,43 +1093,43 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D17" t="n">
-        <v>465.0</v>
+        <v>485.0</v>
       </c>
       <c r="E17" t="n">
-        <v>31.0</v>
+        <v>30.3125</v>
       </c>
       <c r="F17" t="n">
-        <v>3100.0</v>
+        <v>3200.0</v>
       </c>
       <c r="G17" t="n">
-        <v>206.66666666666666</v>
+        <v>200.0</v>
       </c>
       <c r="H17" t="n">
         <v>3700.0</v>
       </c>
       <c r="I17" t="n">
-        <v>246.66666666666666</v>
+        <v>231.25</v>
       </c>
       <c r="J17" t="n">
-        <v>37.06666666666667</v>
+        <v>37.5625</v>
       </c>
       <c r="K17" t="n">
-        <v>34.6</v>
+        <v>35.375</v>
       </c>
       <c r="L17" t="n">
-        <v>32.53333333333333</v>
+        <v>33.3125</v>
       </c>
       <c r="M17" t="n">
         <v>22.0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.404833836858006</v>
+        <v>1.3472222222222223</v>
       </c>
     </row>
     <row r="18">
@@ -1143,43 +1137,43 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D18" t="n">
-        <v>605.0</v>
+        <v>655.0</v>
       </c>
       <c r="E18" t="n">
-        <v>40.333333333333336</v>
+        <v>40.9375</v>
       </c>
       <c r="F18" t="n">
-        <v>5400.0</v>
+        <v>6000.0</v>
       </c>
       <c r="G18" t="n">
-        <v>360.0</v>
+        <v>375.0</v>
       </c>
       <c r="H18" t="n">
-        <v>4850.0</v>
+        <v>5250.0</v>
       </c>
       <c r="I18" t="n">
-        <v>323.3333333333333</v>
+        <v>328.125</v>
       </c>
       <c r="J18" t="n">
-        <v>30.8</v>
+        <v>30.6875</v>
       </c>
       <c r="K18" t="n">
-        <v>48.733333333333334</v>
+        <v>49.1875</v>
       </c>
       <c r="L18" t="n">
-        <v>39.46666666666667</v>
+        <v>38.8125</v>
       </c>
       <c r="M18" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.037037037037037</v>
+        <v>2.040498442367601</v>
       </c>
     </row>
     <row r="19">
@@ -1187,43 +1181,43 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" t="n">
         <v>15.0</v>
       </c>
       <c r="D19" t="n">
-        <v>700.0</v>
+        <v>655.0</v>
       </c>
       <c r="E19" t="n">
+        <v>43.666666666666664</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7350.0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>490.0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6000.0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>400.0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.666666666666668</v>
+      </c>
+      <c r="K19" t="n">
         <v>46.666666666666664</v>
       </c>
-      <c r="F19" t="n">
-        <v>9300.0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>620.0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>7300.0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>486.6666666666667</v>
-      </c>
-      <c r="J19" t="n">
-        <v>45.46666666666667</v>
-      </c>
-      <c r="K19" t="n">
-        <v>44.93333333333333</v>
-      </c>
       <c r="L19" t="n">
-        <v>29.6</v>
+        <v>32.4</v>
       </c>
       <c r="M19" t="n">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9607843137254901</v>
+        <v>2.046875</v>
       </c>
     </row>
     <row r="20">
@@ -1231,43 +1225,43 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="D20" t="n">
-        <v>730.0</v>
+        <v>700.0</v>
       </c>
       <c r="E20" t="n">
-        <v>52.142857142857146</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="F20" t="n">
-        <v>9250.0</v>
+        <v>9300.0</v>
       </c>
       <c r="G20" t="n">
-        <v>660.7142857142857</v>
+        <v>620.0</v>
       </c>
       <c r="H20" t="n">
-        <v>7200.0</v>
+        <v>7300.0</v>
       </c>
       <c r="I20" t="n">
-        <v>514.2857142857143</v>
+        <v>486.6666666666667</v>
       </c>
       <c r="J20" t="n">
-        <v>46.57142857142857</v>
+        <v>45.46666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>49.07142857142857</v>
+        <v>44.93333333333333</v>
       </c>
       <c r="L20" t="n">
-        <v>40.57142857142857</v>
+        <v>29.6</v>
       </c>
       <c r="M20" t="n">
-        <v>26.0</v>
+        <v>23.0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9676549865229112</v>
+        <v>1.9607843137254901</v>
       </c>
     </row>
     <row r="21">
@@ -1275,43 +1269,43 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" t="n">
         <v>14.0</v>
       </c>
       <c r="D21" t="n">
-        <v>580.0</v>
+        <v>730.0</v>
       </c>
       <c r="E21" t="n">
-        <v>41.42857142857143</v>
+        <v>52.142857142857146</v>
       </c>
       <c r="F21" t="n">
-        <v>6000.0</v>
+        <v>9250.0</v>
       </c>
       <c r="G21" t="n">
-        <v>428.57142857142856</v>
+        <v>660.7142857142857</v>
       </c>
       <c r="H21" t="n">
-        <v>4900.0</v>
+        <v>7200.0</v>
       </c>
       <c r="I21" t="n">
-        <v>350.0</v>
+        <v>514.2857142857143</v>
       </c>
       <c r="J21" t="n">
-        <v>31.357142857142858</v>
+        <v>46.57142857142857</v>
       </c>
       <c r="K21" t="n">
-        <v>49.285714285714285</v>
+        <v>49.07142857142857</v>
       </c>
       <c r="L21" t="n">
-        <v>34.0</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="M21" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9463087248322148</v>
+        <v>1.9676549865229112</v>
       </c>
     </row>
     <row r="22">
@@ -1319,43 +1313,43 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D22" t="n">
-        <v>485.0</v>
+        <v>505.0</v>
       </c>
       <c r="E22" t="n">
-        <v>40.416666666666664</v>
+        <v>38.84615384615385</v>
       </c>
       <c r="F22" t="n">
         <v>5050.0</v>
       </c>
       <c r="G22" t="n">
-        <v>420.8333333333333</v>
+        <v>388.46153846153845</v>
       </c>
       <c r="H22" t="n">
         <v>4300.0</v>
       </c>
       <c r="I22" t="n">
-        <v>358.3333333333333</v>
+        <v>330.7692307692308</v>
       </c>
       <c r="J22" t="n">
-        <v>41.583333333333336</v>
+        <v>42.76923076923077</v>
       </c>
       <c r="K22" t="n">
-        <v>32.083333333333336</v>
+        <v>29.615384615384617</v>
       </c>
       <c r="L22" t="n">
-        <v>31.75</v>
+        <v>33.69230769230769</v>
       </c>
       <c r="M22" t="n">
         <v>27.0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4923076923076923</v>
+        <v>1.4346590909090908</v>
       </c>
     </row>
     <row r="23">
@@ -1363,43 +1357,43 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" t="n">
         <v>10.0</v>
       </c>
       <c r="D23" t="n">
-        <v>290.0</v>
+        <v>390.0</v>
       </c>
       <c r="E23" t="n">
-        <v>29.0</v>
+        <v>39.0</v>
       </c>
       <c r="F23" t="n">
-        <v>1900.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G23" t="n">
-        <v>190.0</v>
+        <v>350.0</v>
       </c>
       <c r="H23" t="n">
-        <v>1900.0</v>
+        <v>1800.0</v>
       </c>
       <c r="I23" t="n">
-        <v>190.0</v>
+        <v>180.0</v>
       </c>
       <c r="J23" t="n">
-        <v>54.2</v>
+        <v>35.6</v>
       </c>
       <c r="K23" t="n">
-        <v>19.0</v>
+        <v>54.7</v>
       </c>
       <c r="L23" t="n">
-        <v>36.1</v>
+        <v>38.7</v>
       </c>
       <c r="M23" t="n">
         <v>21.0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.355140186915888</v>
+        <v>1.8483412322274881</v>
       </c>
     </row>
     <row r="24">
@@ -1407,43 +1401,43 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D24" t="n">
-        <v>390.0</v>
+        <v>330.0</v>
       </c>
       <c r="E24" t="n">
-        <v>39.0</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="F24" t="n">
-        <v>3500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="G24" t="n">
-        <v>350.0</v>
+        <v>444.44444444444446</v>
       </c>
       <c r="H24" t="n">
-        <v>1800.0</v>
+        <v>3550.0</v>
       </c>
       <c r="I24" t="n">
-        <v>180.0</v>
+        <v>394.44444444444446</v>
       </c>
       <c r="J24" t="n">
-        <v>35.6</v>
+        <v>42.888888888888886</v>
       </c>
       <c r="K24" t="n">
-        <v>54.7</v>
+        <v>42.666666666666664</v>
       </c>
       <c r="L24" t="n">
-        <v>38.7</v>
+        <v>36.22222222222222</v>
       </c>
       <c r="M24" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.8483412322274881</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
@@ -1451,43 +1445,43 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D25" t="n">
-        <v>290.0</v>
+        <v>390.0</v>
       </c>
       <c r="E25" t="n">
-        <v>36.25</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="F25" t="n">
-        <v>3600.0</v>
+        <v>4300.0</v>
       </c>
       <c r="G25" t="n">
-        <v>450.0</v>
+        <v>477.77777777777777</v>
       </c>
       <c r="H25" t="n">
-        <v>3550.0</v>
+        <v>4100.0</v>
       </c>
       <c r="I25" t="n">
-        <v>443.75</v>
+        <v>455.55555555555554</v>
       </c>
       <c r="J25" t="n">
-        <v>39.125</v>
+        <v>47.333333333333336</v>
       </c>
       <c r="K25" t="n">
-        <v>39.0</v>
+        <v>38.77777777777778</v>
       </c>
       <c r="L25" t="n">
-        <v>31.75</v>
+        <v>32.333333333333336</v>
       </c>
       <c r="M25" t="n">
-        <v>21.0</v>
+        <v>25.0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7159763313609468</v>
+        <v>1.703056768558952</v>
       </c>
     </row>
     <row r="26">
@@ -1495,43 +1489,43 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D26" t="n">
-        <v>350.0</v>
+        <v>315.0</v>
       </c>
       <c r="E26" t="n">
-        <v>43.75</v>
+        <v>45.0</v>
       </c>
       <c r="F26" t="n">
-        <v>3900.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G26" t="n">
-        <v>487.5</v>
+        <v>500.0</v>
       </c>
       <c r="H26" t="n">
-        <v>3800.0</v>
+        <v>2650.0</v>
       </c>
       <c r="I26" t="n">
-        <v>475.0</v>
+        <v>378.57142857142856</v>
       </c>
       <c r="J26" t="n">
-        <v>47.75</v>
+        <v>46.714285714285715</v>
       </c>
       <c r="K26" t="n">
-        <v>33.0</v>
+        <v>34.714285714285715</v>
       </c>
       <c r="L26" t="n">
-        <v>30.875</v>
+        <v>32.714285714285715</v>
       </c>
       <c r="M26" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7073170731707317</v>
+        <v>1.6935483870967742</v>
       </c>
     </row>
     <row r="27">
@@ -1539,43 +1533,43 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" t="n">
         <v>7.0</v>
       </c>
       <c r="D27" t="n">
-        <v>315.0</v>
+        <v>350.0</v>
       </c>
       <c r="E27" t="n">
-        <v>45.0</v>
+        <v>50.0</v>
       </c>
       <c r="F27" t="n">
-        <v>3500.0</v>
+        <v>4950.0</v>
       </c>
       <c r="G27" t="n">
-        <v>500.0</v>
+        <v>707.1428571428571</v>
       </c>
       <c r="H27" t="n">
-        <v>2650.0</v>
+        <v>3600.0</v>
       </c>
       <c r="I27" t="n">
-        <v>378.57142857142856</v>
+        <v>514.2857142857143</v>
       </c>
       <c r="J27" t="n">
-        <v>46.714285714285715</v>
+        <v>43.42857142857143</v>
       </c>
       <c r="K27" t="n">
-        <v>34.714285714285715</v>
+        <v>41.57142857142857</v>
       </c>
       <c r="L27" t="n">
-        <v>32.714285714285715</v>
+        <v>27.857142857142858</v>
       </c>
       <c r="M27" t="n">
-        <v>26.0</v>
+        <v>23.0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.6935483870967742</v>
+        <v>2.095808383233533</v>
       </c>
     </row>
     <row r="28">
@@ -1583,43 +1577,43 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D28" t="n">
-        <v>350.0</v>
+        <v>215.0</v>
       </c>
       <c r="E28" t="n">
-        <v>50.0</v>
+        <v>35.833333333333336</v>
       </c>
       <c r="F28" t="n">
-        <v>4950.0</v>
+        <v>2150.0</v>
       </c>
       <c r="G28" t="n">
-        <v>707.1428571428571</v>
+        <v>358.3333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>3600.0</v>
+        <v>1800.0</v>
       </c>
       <c r="I28" t="n">
-        <v>514.2857142857143</v>
+        <v>300.0</v>
       </c>
       <c r="J28" t="n">
-        <v>43.42857142857143</v>
+        <v>35.0</v>
       </c>
       <c r="K28" t="n">
-        <v>41.57142857142857</v>
+        <v>47.666666666666664</v>
       </c>
       <c r="L28" t="n">
-        <v>27.857142857142858</v>
+        <v>38.666666666666664</v>
       </c>
       <c r="M28" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.095808383233533</v>
+        <v>1.4827586206896552</v>
       </c>
     </row>
     <row r="29">
@@ -1627,22 +1621,22 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="n">
         <v>6.0</v>
       </c>
       <c r="D29" t="n">
-        <v>215.0</v>
+        <v>290.0</v>
       </c>
       <c r="E29" t="n">
-        <v>35.833333333333336</v>
+        <v>48.333333333333336</v>
       </c>
       <c r="F29" t="n">
-        <v>2150.0</v>
+        <v>3300.0</v>
       </c>
       <c r="G29" t="n">
-        <v>358.3333333333333</v>
+        <v>550.0</v>
       </c>
       <c r="H29" t="n">
         <v>1800.0</v>
@@ -1651,19 +1645,19 @@
         <v>300.0</v>
       </c>
       <c r="J29" t="n">
-        <v>35.0</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>47.666666666666664</v>
+        <v>33.0</v>
       </c>
       <c r="L29" t="n">
-        <v>38.666666666666664</v>
+        <v>32.833333333333336</v>
       </c>
       <c r="M29" t="n">
         <v>24.0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4827586206896552</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="30">
@@ -1671,43 +1665,43 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" t="n">
         <v>6.0</v>
       </c>
       <c r="D30" t="n">
-        <v>290.0</v>
+        <v>270.0</v>
       </c>
       <c r="E30" t="n">
-        <v>48.333333333333336</v>
+        <v>45.0</v>
       </c>
       <c r="F30" t="n">
-        <v>3300.0</v>
+        <v>3700.0</v>
       </c>
       <c r="G30" t="n">
-        <v>550.0</v>
+        <v>616.6666666666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1800.0</v>
+        <v>3400.0</v>
       </c>
       <c r="I30" t="n">
-        <v>300.0</v>
+        <v>566.6666666666666</v>
       </c>
       <c r="J30" t="n">
-        <v>64.16666666666667</v>
+        <v>31.666666666666668</v>
       </c>
       <c r="K30" t="n">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="L30" t="n">
-        <v>32.833333333333336</v>
+        <v>32.0</v>
       </c>
       <c r="M30" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.0</v>
+        <v>1.9708029197080292</v>
       </c>
     </row>
     <row r="31">
@@ -1715,43 +1709,43 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D31" t="n">
-        <v>270.0</v>
+        <v>200.0</v>
       </c>
       <c r="E31" t="n">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="F31" t="n">
-        <v>3700.0</v>
+        <v>2800.0</v>
       </c>
       <c r="G31" t="n">
-        <v>616.6666666666666</v>
+        <v>560.0</v>
       </c>
       <c r="H31" t="n">
-        <v>3400.0</v>
+        <v>2700.0</v>
       </c>
       <c r="I31" t="n">
-        <v>566.6666666666666</v>
+        <v>540.0</v>
       </c>
       <c r="J31" t="n">
-        <v>31.666666666666668</v>
+        <v>39.2</v>
       </c>
       <c r="K31" t="n">
-        <v>36.0</v>
+        <v>26.6</v>
       </c>
       <c r="L31" t="n">
-        <v>32.0</v>
+        <v>26.6</v>
       </c>
       <c r="M31" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.9708029197080292</v>
+        <v>1.639344262295082</v>
       </c>
     </row>
     <row r="32">
@@ -1759,43 +1753,43 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" t="n">
         <v>5.0</v>
       </c>
       <c r="D32" t="n">
-        <v>200.0</v>
+        <v>220.0</v>
       </c>
       <c r="E32" t="n">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="F32" t="n">
-        <v>2800.0</v>
+        <v>3100.0</v>
       </c>
       <c r="G32" t="n">
-        <v>560.0</v>
+        <v>620.0</v>
       </c>
       <c r="H32" t="n">
-        <v>2700.0</v>
+        <v>2600.0</v>
       </c>
       <c r="I32" t="n">
-        <v>540.0</v>
+        <v>520.0</v>
       </c>
       <c r="J32" t="n">
-        <v>39.2</v>
+        <v>42.6</v>
       </c>
       <c r="K32" t="n">
-        <v>26.6</v>
+        <v>50.2</v>
       </c>
       <c r="L32" t="n">
-        <v>26.6</v>
+        <v>54.8</v>
       </c>
       <c r="M32" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.639344262295082</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="33">
@@ -1803,43 +1797,43 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D33" t="n">
-        <v>220.0</v>
+        <v>120.0</v>
       </c>
       <c r="E33" t="n">
-        <v>44.0</v>
+        <v>30.0</v>
       </c>
       <c r="F33" t="n">
-        <v>3100.0</v>
+        <v>800.0</v>
       </c>
       <c r="G33" t="n">
-        <v>620.0</v>
+        <v>200.0</v>
       </c>
       <c r="H33" t="n">
-        <v>2600.0</v>
+        <v>800.0</v>
       </c>
       <c r="I33" t="n">
-        <v>520.0</v>
+        <v>200.0</v>
       </c>
       <c r="J33" t="n">
-        <v>42.6</v>
+        <v>38.75</v>
       </c>
       <c r="K33" t="n">
-        <v>50.2</v>
+        <v>53.5</v>
       </c>
       <c r="L33" t="n">
-        <v>54.8</v>
+        <v>40.0</v>
       </c>
       <c r="M33" t="n">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.0</v>
+        <v>1.3793103448275863</v>
       </c>
     </row>
     <row r="34">
@@ -1847,43 +1841,43 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" t="n">
         <v>4.0</v>
       </c>
       <c r="D34" t="n">
-        <v>120.0</v>
+        <v>230.0</v>
       </c>
       <c r="E34" t="n">
-        <v>30.0</v>
+        <v>57.5</v>
       </c>
       <c r="F34" t="n">
-        <v>800.0</v>
+        <v>3100.0</v>
       </c>
       <c r="G34" t="n">
-        <v>200.0</v>
+        <v>775.0</v>
       </c>
       <c r="H34" t="n">
-        <v>800.0</v>
+        <v>1650.0</v>
       </c>
       <c r="I34" t="n">
-        <v>200.0</v>
+        <v>412.5</v>
       </c>
       <c r="J34" t="n">
-        <v>38.75</v>
+        <v>48.75</v>
       </c>
       <c r="K34" t="n">
-        <v>53.5</v>
+        <v>40.25</v>
       </c>
       <c r="L34" t="n">
-        <v>40.0</v>
+        <v>48.75</v>
       </c>
       <c r="M34" t="n">
         <v>21.0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.3793103448275863</v>
+        <v>2.6436781609195403</v>
       </c>
     </row>
     <row r="35">
@@ -1891,43 +1885,43 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" t="n">
         <v>4.0</v>
       </c>
       <c r="D35" t="n">
-        <v>230.0</v>
+        <v>120.0</v>
       </c>
       <c r="E35" t="n">
-        <v>57.5</v>
+        <v>30.0</v>
       </c>
       <c r="F35" t="n">
-        <v>3100.0</v>
+        <v>1100.0</v>
       </c>
       <c r="G35" t="n">
-        <v>775.0</v>
+        <v>275.0</v>
       </c>
       <c r="H35" t="n">
-        <v>1650.0</v>
+        <v>900.0</v>
       </c>
       <c r="I35" t="n">
-        <v>412.5</v>
+        <v>225.0</v>
       </c>
       <c r="J35" t="n">
-        <v>48.75</v>
+        <v>44.0</v>
       </c>
       <c r="K35" t="n">
-        <v>40.25</v>
+        <v>23.75</v>
       </c>
       <c r="L35" t="n">
-        <v>48.75</v>
+        <v>45.0</v>
       </c>
       <c r="M35" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.6436781609195403</v>
+        <v>1.2244897959183674</v>
       </c>
     </row>
     <row r="36">
@@ -1935,43 +1929,43 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" t="n">
         <v>4.0</v>
       </c>
       <c r="D36" t="n">
-        <v>120.0</v>
+        <v>200.0</v>
       </c>
       <c r="E36" t="n">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="F36" t="n">
-        <v>1100.0</v>
+        <v>2700.0</v>
       </c>
       <c r="G36" t="n">
-        <v>275.0</v>
+        <v>675.0</v>
       </c>
       <c r="H36" t="n">
-        <v>900.0</v>
+        <v>2700.0</v>
       </c>
       <c r="I36" t="n">
-        <v>225.0</v>
+        <v>675.0</v>
       </c>
       <c r="J36" t="n">
-        <v>44.0</v>
+        <v>45.5</v>
       </c>
       <c r="K36" t="n">
-        <v>23.75</v>
+        <v>28.25</v>
       </c>
       <c r="L36" t="n">
-        <v>45.0</v>
+        <v>31.25</v>
       </c>
       <c r="M36" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.2244897959183674</v>
+        <v>2.247191011235955</v>
       </c>
     </row>
     <row r="37">
@@ -1979,7 +1973,7 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C37" t="n">
         <v>3.0</v>
@@ -2023,7 +2017,7 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C38" t="n">
         <v>3.0</v>
@@ -2067,43 +2061,43 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" t="n">
         <v>3.0</v>
       </c>
       <c r="D39" t="n">
-        <v>160.0</v>
+        <v>120.0</v>
       </c>
       <c r="E39" t="n">
-        <v>53.333333333333336</v>
+        <v>40.0</v>
       </c>
       <c r="F39" t="n">
-        <v>2400.0</v>
+        <v>800.0</v>
       </c>
       <c r="G39" t="n">
-        <v>800.0</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="H39" t="n">
-        <v>2500.0</v>
+        <v>1300.0</v>
       </c>
       <c r="I39" t="n">
-        <v>833.3333333333334</v>
+        <v>433.3333333333333</v>
       </c>
       <c r="J39" t="n">
-        <v>36.0</v>
+        <v>46.333333333333336</v>
       </c>
       <c r="K39" t="n">
-        <v>32.0</v>
+        <v>18.0</v>
       </c>
       <c r="L39" t="n">
-        <v>36.0</v>
+        <v>32.333333333333336</v>
       </c>
       <c r="M39" t="n">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.2535211267605635</v>
+        <v>1.4457831325301205</v>
       </c>
     </row>
     <row r="40">
@@ -2111,43 +2105,43 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" t="n">
         <v>3.0</v>
       </c>
       <c r="D40" t="n">
-        <v>120.0</v>
+        <v>130.0</v>
       </c>
       <c r="E40" t="n">
-        <v>40.0</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="F40" t="n">
-        <v>800.0</v>
+        <v>2100.0</v>
       </c>
       <c r="G40" t="n">
-        <v>266.6666666666667</v>
+        <v>700.0</v>
       </c>
       <c r="H40" t="n">
-        <v>1300.0</v>
+        <v>1400.0</v>
       </c>
       <c r="I40" t="n">
-        <v>433.3333333333333</v>
+        <v>466.6666666666667</v>
       </c>
       <c r="J40" t="n">
-        <v>46.333333333333336</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="L40" t="n">
-        <v>32.333333333333336</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="M40" t="n">
-        <v>27.0</v>
+        <v>23.0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.4457831325301205</v>
+        <v>1.8309859154929577</v>
       </c>
     </row>
     <row r="41">
@@ -2155,43 +2149,43 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D41" t="n">
-        <v>130.0</v>
+        <v>85.0</v>
       </c>
       <c r="E41" t="n">
-        <v>43.333333333333336</v>
+        <v>42.5</v>
       </c>
       <c r="F41" t="n">
-        <v>2100.0</v>
+        <v>900.0</v>
       </c>
       <c r="G41" t="n">
-        <v>700.0</v>
+        <v>450.0</v>
       </c>
       <c r="H41" t="n">
-        <v>1400.0</v>
+        <v>900.0</v>
       </c>
       <c r="I41" t="n">
-        <v>466.6666666666667</v>
+        <v>450.0</v>
       </c>
       <c r="J41" t="n">
-        <v>6.666666666666667</v>
+        <v>24.0</v>
       </c>
       <c r="K41" t="n">
-        <v>21.0</v>
+        <v>16.5</v>
       </c>
       <c r="L41" t="n">
-        <v>6.666666666666667</v>
+        <v>16.5</v>
       </c>
       <c r="M41" t="n">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.8309859154929577</v>
+        <v>1.6346153846153846</v>
       </c>
     </row>
     <row r="42">
@@ -2199,7 +2193,7 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C42" t="n">
         <v>2.0</v>
@@ -2243,7 +2237,7 @@
         <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C43" t="n">
         <v>2.0</v>
@@ -2287,7 +2281,7 @@
         <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C44" t="n">
         <v>2.0</v>
@@ -2331,7 +2325,7 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" t="n">
         <v>1.0</v>
@@ -2375,43 +2369,43 @@
         <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" t="n">
         <v>1.0</v>
       </c>
       <c r="D46" t="n">
-        <v>65.0</v>
+        <v>70.0</v>
       </c>
       <c r="E46" t="n">
-        <v>65.0</v>
+        <v>70.0</v>
       </c>
       <c r="F46" t="n">
-        <v>900.0</v>
+        <v>1200.0</v>
       </c>
       <c r="G46" t="n">
-        <v>900.0</v>
+        <v>1200.0</v>
       </c>
       <c r="H46" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="I46" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="J46" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="K46" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M46" t="n">
         <v>22.0</v>
       </c>
-      <c r="L46" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>29.0</v>
-      </c>
       <c r="N46" t="n">
-        <v>2.2413793103448274</v>
+        <v>3.1818181818181817</v>
       </c>
     </row>
     <row r="47">
@@ -2419,43 +2413,43 @@
         <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C47" t="n">
         <v>1.0</v>
       </c>
       <c r="D47" t="n">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="E47" t="n">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="F47" t="n">
-        <v>1200.0</v>
+        <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>1200.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" t="n">
-        <v>600.0</v>
+        <v>100.0</v>
       </c>
       <c r="I47" t="n">
-        <v>600.0</v>
+        <v>100.0</v>
       </c>
       <c r="J47" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="K47" t="n">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="L47" t="n">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="M47" t="n">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1818181818181817</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="48">
@@ -2463,43 +2457,43 @@
         <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C48" t="n">
         <v>1.0</v>
       </c>
       <c r="D48" t="n">
-        <v>20.0</v>
+        <v>90.0</v>
       </c>
       <c r="E48" t="n">
-        <v>20.0</v>
+        <v>90.0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H48" t="n">
-        <v>100.0</v>
+        <v>800.0</v>
       </c>
       <c r="I48" t="n">
-        <v>100.0</v>
+        <v>800.0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="K48" t="n">
-        <v>16.0</v>
+        <v>68.0</v>
       </c>
       <c r="L48" t="n">
-        <v>16.0</v>
+        <v>36.0</v>
       </c>
       <c r="M48" t="n">
-        <v>16.0</v>
+        <v>26.0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.25</v>
+        <v>3.4615384615384617</v>
       </c>
     </row>
     <row r="49">
@@ -2507,86 +2501,42 @@
         <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C49" t="n">
         <v>1.0</v>
       </c>
       <c r="D49" t="n">
-        <v>90.0</v>
+        <v>50.0</v>
       </c>
       <c r="E49" t="n">
-        <v>90.0</v>
+        <v>50.0</v>
       </c>
       <c r="F49" t="n">
-        <v>2000.0</v>
+        <v>400.0</v>
       </c>
       <c r="G49" t="n">
-        <v>2000.0</v>
+        <v>400.0</v>
       </c>
       <c r="H49" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="I49" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="J49" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="K49" t="n">
-        <v>68.0</v>
+        <v>41.0</v>
       </c>
       <c r="L49" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="M49" t="n">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4615384615384617</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="N50" t="n">
         <v>1.5151515151515151</v>
       </c>
     </row>
